--- a/siting_compliance_26Sep/outputs/tables/siting_results.xlsx
+++ b/siting_compliance_26Sep/outputs/tables/siting_results.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix_2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distances_2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail_2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix_2016" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail_2016" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Habitation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protected_areas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_sources" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matrix_2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Distances_2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detail_2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Matrix_2016" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Detail_2016" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Habitation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Airports" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Protected_areas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Rules" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Data_sources" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Parameters" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,17 +576,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
+          <t>Airport / airbase</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,17 +610,17 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
+          <t>Airport / airbase</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -897,22 +897,17 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Pond, Airport / airbase, Flood plain (100-year)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Habitation</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -1019,12 +1014,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>River, Airport / airbase, Flood plain (100-year)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Habitation</t>
+          <t>River, Habitation, Airport / airbase, Flood plain (100-year)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1623,7 +1613,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'small_airport', 'medium_airport', 'large_airport'}</t>
+          <t>{'large_airport', 'medium_airport', 'small_airport'}</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1673,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/data</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/data</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1745,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/figures</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/figures</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1805,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'AHM-01': ('confirmed', 'dense housing on the east / south-east edge; industrial units elsewhere (excluded)'), 'AHM-02': ('uncertain', 'Pirana STP to the west (excluded); small structures to the north and south-east may be sheds or huts'), 'AHM-03': ('uncertain', 'many small structures in the walled yard just north; may be a waste-handling / scrap yard, not homes'), 'BHJ-01': ('confirmed', 'houses of the residential area to the south'), 'BHV-01': ('none', 'no buildings inside the 200 m ring'), 'GNR-01': ('confirmed', 'dense cluster of small dwellings along the west edge'), 'JAM-01': ('confirmed', 'residential plots and houses to the south and west'), 'MEH-01': ('confirmed', 'houses to the north-west'), 'RAJ-01': ('none', 'structures in the ring are the processing-plant buildings on the east side'), 'SUR-01': ('confirmed', 'most mapped structures are Bhatar STP units, but dense housing lies inside the ring to the south-west'), 'SUR-02': ('uncertain', 'small cluster south of the southern cell; north side is industrial (excluded)'), 'VAD-01': ('likely', 'scattered houses / farm buildings to the north and west'), 'VAD-02': ('confirmed', 'apartments and houses to the west and south'), 'VAP-01': ('uncertain', 'a few small structures to the south-east; industrial buildings excluded')}</t>
+          <t>{'AHM-01': ('confirmed', 'dense housing on the east / south-east edge; industrial units elsewhere (excluded)'), 'AHM-02': ('not residential', 'student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)'), 'AHM-03': ('not residential', 'student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)'), 'BHJ-01': ('confirmed', 'houses of the residential area to the south'), 'BHV-01': ('none', 'no buildings inside the 200 m ring'), 'GNR-01': ('confirmed', 'dense cluster of small dwellings along the west edge'), 'JAM-01': ('confirmed', 'residential plots and houses to the south and west'), 'MEH-01': ('confirmed', 'houses to the north-west'), 'RAJ-01': ('none', 'structures in the ring are the processing-plant buildings on the east side'), 'SUR-01': ('confirmed', 'most mapped structures are Bhatar STP units, but dense housing lies inside the ring to the south-west'), 'SUR-02': ('not residential', 'student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial'), 'VAD-01': ('likely', 'scattered houses / farm buildings to the north and west'), 'VAD-02': ('confirmed', 'apartments and houses to the west and south'), 'VAP-01': ('confirmed', 'student imagery check 26 Sep: residential buildings within 200 m to the south-east')}</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1841,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'motorway_link', 'primary_link', 'motorway', 'primary', 'trunk_link', 'trunk'}</t>
+          <t>{'motorway', 'primary', 'primary_link', 'trunk_link', 'trunk', 'motorway_link'}</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1901,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/home/claude/Locations of landfills in gujurat Completed.kml</t>
+          <t>/home/user/waste-managment-project-1/Locations of landfills in gujurat completer.kml</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1925,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/logs</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/logs</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1949,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'RAJ', 'AHM', 'VAD', 'SUR', 'BHV'}</t>
+          <t>{'BHV', 'SUR', 'RAJ', 'VAD', 'AHM'}</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1973,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'stream_pool', 'fountain', 'canal', 'ditch', 'stream', 'moat', 'river', 'wastewater', 'drain'}</t>
+          <t>{'drain', 'wastewater', 'river', 'stream_pool', 'moat', 'fountain', 'stream', 'ditch', 'canal'}</t>
         </is>
       </c>
     </row>
@@ -2007,7 +1997,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/outputs</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2057,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'', 'lake', 'basin', 'lagoon', 'pond', 'reservoir', 'oxbow'}</t>
+          <t>{'', 'lagoon', 'reservoir', 'oxbow', 'lake', 'basin', 'pond'}</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2069,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/home/claude</t>
+          <t>/home/user/waste-managment-project-1</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2081,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/data/raw</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/data/raw</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2093,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2105,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/scripts</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/scripts</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2117,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/outputs/sites</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/sites</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2129,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/home/claude/siting_compliance_26Sep/outputs/tables</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/tables</t>
         </is>
       </c>
     </row>
@@ -2437,9 +2427,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2486,17 +2476,17 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
+          <t>Airport / airbase</t>
         </is>
       </c>
     </row>
@@ -2526,9 +2516,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2575,17 +2565,17 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
+          <t>Airport / airbase</t>
         </is>
       </c>
     </row>
@@ -3253,9 +3243,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3302,10 +3292,10 @@
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>10</v>
@@ -3315,11 +3305,6 @@
           <t>Pond, Airport / airbase, Flood plain (100-year)</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Habitation</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3530,9 +3515,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3576,10 +3561,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
@@ -3589,12 +3574,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>River, Airport / airbase, Flood plain (100-year)</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Habitation</t>
+          <t>River, Habitation, Airport / airbase, Flood plain (100-year)</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3810,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -3893,7 +3873,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -4379,7 +4359,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -4568,7 +4548,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4629,7 +4609,7 @@
     <col width="58" customWidth="1" min="16" max="16"/>
     <col width="48" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
@@ -5750,9 +5730,9 @@
       <c r="K17" t="n">
         <v>48</v>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5767,12 +5747,12 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Pirana STP to the west (excluded); small structures to the north and south-east may be sheds or huts</t>
+          <t>student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -6483,9 +6463,9 @@
       <c r="K29" t="n">
         <v>146</v>
       </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -6500,12 +6480,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>many small structures in the walled yard just north; may be a waste-handling / scrap yard, not homes</t>
+          <t>student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -12333,9 +12313,9 @@
       <c r="K125" t="n">
         <v>33</v>
       </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12350,12 +12330,12 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>small cluster south of the southern cell; north side is industrial (excluded)</t>
+          <t>student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial</t>
         </is>
       </c>
       <c r="U125" t="n">
@@ -14532,9 +14512,9 @@
       <c r="K161" t="n">
         <v>7</v>
       </c>
-      <c r="L161" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14549,12 +14529,12 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>a few small structures to the south-east; industrial buildings excluded</t>
+          <t>student imagery check 26 Sep: residential buildings within 200 m to the south-east</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15032,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15277,9 +15257,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -15326,17 +15306,17 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase, Flood plain (100-year)</t>
+          <t>Airport / airbase, Flood plain (100-year)</t>
         </is>
       </c>
     </row>
@@ -15366,9 +15346,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15415,17 +15395,17 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
+          <t>Airport / airbase</t>
         </is>
       </c>
     </row>
@@ -16093,9 +16073,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16142,10 +16122,10 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
         <v>10</v>
@@ -16153,11 +16133,6 @@
       <c r="S12" t="inlineStr">
         <is>
           <t>Airport / airbase, Flood plain (100-year)</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Habitation</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16440,7 @@
     <col width="58" customWidth="1" min="16" max="16"/>
     <col width="48" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="45" customWidth="1" min="22" max="22"/>
@@ -17586,9 +17561,9 @@
       <c r="K17" t="n">
         <v>268</v>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -17603,12 +17578,12 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Pirana STP to the west (excluded); small structures to the north and south-east may be sheds or huts</t>
+          <t>student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -18319,9 +18294,9 @@
       <c r="K29" t="n">
         <v>74</v>
       </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -18336,12 +18311,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>many small structures in the walled yard just north; may be a waste-handling / scrap yard, not homes</t>
+          <t>student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -24159,9 +24134,9 @@
       <c r="K125" t="n">
         <v>36</v>
       </c>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24176,12 +24151,12 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>small cluster south of the southern cell; north side is industrial (excluded)</t>
+          <t>student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial</t>
         </is>
       </c>
       <c r="U125" t="n">
@@ -26375,12 +26350,12 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>a few small structures to the south-east; industrial buildings excluded</t>
+          <t>student imagery check 26 Sep: residential buildings within 200 m to the south-east</t>
         </is>
       </c>
     </row>
@@ -26877,7 +26852,7 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="25" customWidth="1" min="22" max="22"/>
@@ -27271,12 +27246,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Pirana STP to the west (excluded); small structures to the north and south-east may be sheds or huts</t>
+          <t>student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -27368,12 +27343,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Pirana STP to the west (excluded); small structures to the north and south-east may be sheds or huts</t>
+          <t>student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -27465,12 +27440,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>many small structures in the walled yard just north; may be a waste-handling / scrap yard, not homes</t>
+          <t>student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -27562,12 +27537,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>many small structures in the walled yard just north; may be a waste-handling / scrap yard, not homes</t>
+          <t>student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -29003,12 +28978,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>small cluster south of the southern cell; north side is industrial (excluded)</t>
+          <t>student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -29092,12 +29067,12 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>not residential</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>small cluster south of the southern cell; north side is industrial (excluded)</t>
+          <t>student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -29570,12 +29545,12 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>a few small structures to the south-east; industrial buildings excluded</t>
+          <t>student imagery check 26 Sep: residential buildings within 200 m to the south-east</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -29656,12 +29631,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>a few small structures to the south-east; industrial buildings excluded</t>
+          <t>student imagery check 26 Sep: residential buildings within 200 m to the south-east</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">

--- a/siting_compliance_26Sep/outputs/tables/siting_results.xlsx
+++ b/siting_compliance_26Sep/outputs/tables/siting_results.xlsx
@@ -471,7 +471,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -753,25 +753,20 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Highway (NH / SH), Habitation, Airport / airbase</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Critical habitat / eco-fragile area</t>
+          <t>Highway (NH / SH), Habitation, Airport / airbase, Critical habitat / eco-fragile area</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1420,7 +1415,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1574,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1613,7 +1608,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'large_airport', 'medium_airport', 'small_airport'}</t>
+          <t>{'small_airport', 'medium_airport', 'large_airport'}</t>
         </is>
       </c>
     </row>
@@ -1728,442 +1723,454 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FACILITY_BUFFER</t>
+          <t>ESZ_REVIEW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>{'JAM-01': ('inside ESZ', 'student check 26 Sep: the landfill lies in the eco-sensitive zone of Khijadiya Wildlife Sanctuary (5.4 km)')}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FIG</t>
+          <t>FACILITY_BUFFER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/figures</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FLOOD_MIN_DEPTH</t>
+          <t>FIG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/figures</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FLOOD_MIN_FRAC</t>
+          <t>FLOOD_MIN_DEPTH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GHSL_FUN_URL</t>
+          <t>FLOOD_MIN_FRAC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://jeodpp.jrc.ec.europa.eu/ftp/jrc-opendata/GHSL/GHS_BUILT_C_GLOBE_R2023A/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10/V1-0/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10_V1_0/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10_V1_0.tif</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GUJARAT_BBOX</t>
+          <t>GHSL_FUN_URL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(19.8, 68.0, 24.9, 74.6)</t>
+          <t>https://jeodpp.jrc.ec.europa.eu/ftp/jrc-opendata/GHSL/GHS_BUILT_C_GLOBE_R2023A/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10/V1-0/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10_V1_0/GHS_BUILT_C_FUN_E2018_GLOBE_R2023A_54009_10_V1_0.tif</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HABITATION_REVIEW</t>
+          <t>GUJARAT_BBOX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'AHM-01': ('confirmed', 'dense housing on the east / south-east edge; industrial units elsewhere (excluded)'), 'AHM-02': ('not residential', 'student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)'), 'AHM-03': ('not residential', 'student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)'), 'BHJ-01': ('confirmed', 'houses of the residential area to the south'), 'BHV-01': ('none', 'no buildings inside the 200 m ring'), 'GNR-01': ('confirmed', 'dense cluster of small dwellings along the west edge'), 'JAM-01': ('confirmed', 'residential plots and houses to the south and west'), 'MEH-01': ('confirmed', 'houses to the north-west'), 'RAJ-01': ('none', 'structures in the ring are the processing-plant buildings on the east side'), 'SUR-01': ('confirmed', 'most mapped structures are Bhatar STP units, but dense housing lies inside the ring to the south-west'), 'SUR-02': ('not residential', 'student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial'), 'VAD-01': ('likely', 'scattered houses / farm buildings to the north and west'), 'VAD-02': ('confirmed', 'apartments and houses to the west and south'), 'VAP-01': ('confirmed', 'student imagery check 26 Sep: residential buildings within 200 m to the south-east')}</t>
+          <t>(19.8, 68.0, 24.9, 74.6)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HAB_MIN_BUILDINGS</t>
+          <t>HABITATION_REVIEW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>{'AHM-01': ('confirmed', 'dense housing on the east / south-east edge; industrial units elsewhere (excluded)'), 'AHM-02': ('not residential', 'student imagery check 26 Sep: structures within 200 m are not dwellings (Pirana STP to the west, sheds north and south-east)'), 'AHM-03': ('not residential', 'student imagery check 26 Sep: structures in the walled yard just north are not dwellings (waste-handling / scrap yard)'), 'BHJ-01': ('confirmed', 'houses of the residential area to the south'), 'BHV-01': ('none', 'no buildings inside the 200 m ring'), 'GNR-01': ('confirmed', 'dense cluster of small dwellings along the west edge'), 'JAM-01': ('confirmed', 'residential plots and houses to the south and west'), 'MEH-01': ('confirmed', 'houses to the north-west'), 'RAJ-01': ('none', 'structures in the ring are the processing-plant buildings on the east side'), 'SUR-01': ('confirmed', 'most mapped structures are Bhatar STP units, but dense housing lies inside the ring to the south-west'), 'SUR-02': ('not residential', 'student imagery check 26 Sep: the cluster south of the southern cell is not residential; north side industrial'), 'VAD-01': ('likely', 'scattered houses / farm buildings to the north and west'), 'VAD-02': ('confirmed', 'apartments and houses to the west and south'), 'VAP-01': ('confirmed', 'student imagery check 26 Sep: residential buildings within 200 m to the south-east')}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HAB_SENS</t>
+          <t>HAB_MIN_BUILDINGS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(1, 5, 20)</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HIGHWAY_CLASSES</t>
+          <t>HAB_SENS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'motorway', 'primary', 'primary_link', 'trunk_link', 'trunk', 'motorway_link'}</t>
+          <t>(1, 5, 20)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HIGHWAY_REF_REGEX</t>
+          <t>HIGHWAY_CLASSES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(?&lt;![A-Za-z])(NH|SH|NE)(?![A-Za-z])</t>
+          <t>{'trunk_link', 'motorway', 'primary', 'trunk', 'motorway_link', 'primary_link'}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JRC_FLOOD_CLIPS</t>
+          <t>HIGHWAY_REF_REGEX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['ID178_N30_E60_RP100_depth_gujarat.tif', 'ID184_N30_E70_RP100_depth_gujarat.tif']</t>
+          <t>(?&lt;![A-Za-z])(NH|SH|NE)(?![A-Za-z])</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JRC_PERM_CLIPS</t>
+          <t>JRC_FLOOD_CLIPS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['ID178_N30_E60_permanent_water_gujarat.tif', 'ID184_N30_E70_permanent_water_gujarat.tif']</t>
+          <t>['ID178_N30_E60_RP100_depth_gujarat.tif', 'ID184_N30_E70_RP100_depth_gujarat.tif']</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JRC_TILES</t>
+          <t>JRC_PERM_CLIPS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>('ID178_N30_E60', 'ID184_N30_E70')</t>
+          <t>['ID178_N30_E60_permanent_water_gujarat.tif', 'ID184_N30_E70_permanent_water_gujarat.tif']</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KML</t>
+          <t>JRC_TILES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/Locations of landfills in gujurat completer.kml</t>
+          <t>('ID178_N30_E60', 'ID184_N30_E70')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LOCAL_RADIUS</t>
+          <t>KML</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>/home/user/waste-managment-project-1/Locations of landfills in gujurat completer.kml</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LOGS</t>
+          <t>LOCAL_RADIUS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/logs</t>
+          <t>2500.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAIN_EPOCH</t>
+          <t>LOGS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/logs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAJOR</t>
+          <t>MAIN_EPOCH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'BHV', 'SUR', 'RAJ', 'VAD', 'AHM'}</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MIN_POND_M2</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>{'BHV', 'SUR', 'AHM', 'VAD', 'RAJ'}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOT_POND</t>
+          <t>MIN_POND_M2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'drain', 'wastewater', 'river', 'stream_pool', 'moat', 'fountain', 'stream', 'ditch', 'canal'}</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OURAIRPORTS_URL</t>
+          <t>NOT_POND</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://davidmegginson.github.io/ourairports-data/airports.csv</t>
+          <t>{'canal', 'fountain', 'stream', 'ditch', 'wastewater', 'drain', 'river', 'moat', 'stream_pool'}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>OURAIRPORTS_URL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs</t>
+          <t>https://davidmegginson.github.io/ourairports-data/airports.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OVERPASS_URLS</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['https://maps.mail.ru/osm/tools/overpass/api/interpreter', 'https://overpass-api.de/api/interpreter', 'https://overpass.kumi.systems/api/interpreter']</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OVERTURE_BUCKET</t>
+          <t>OVERPASS_URLS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>s3://overturemaps-us-west-2/release/{rel}/theme=buildings/type=building/*</t>
+          <t>['https://maps.mail.ru/osm/tools/overpass/api/interpreter', 'https://overpass-api.de/api/interpreter', 'https://overpass.kumi.systems/api/interpreter']</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OVERTURE_RELEASE</t>
+          <t>OVERTURE_BUCKET</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>s3://overturemaps-us-west-2/release/{rel}/theme=buildings/type=building/*</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PARK_LEISURE</t>
+          <t>OVERTURE_RELEASE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'park', 'recreation_ground'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POND_WATER_TYPES</t>
+          <t>PARK_LEISURE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'', 'lagoon', 'reservoir', 'oxbow', 'lake', 'basin', 'pond'}</t>
+          <t>{'recreation_ground', 'park'}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PROJECT</t>
+          <t>POND_WATER_TYPES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1</t>
+          <t>{'', 'pond', 'reservoir', 'oxbow', 'lake', 'lagoon', 'basin'}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RAW</t>
+          <t>PROJECT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/data/raw</t>
+          <t>/home/user/waste-managment-project-1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>RAW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/data/raw</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRIPTS</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/scripts</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SITES_OUT</t>
+          <t>SCRIPTS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/sites</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/scripts</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TABLES</t>
+          <t>SITES_OUT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/tables</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/sites</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TANK_COMPACTNESS</t>
+          <t>TABLES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>/home/user/waste-managment-project-1/siting_compliance_26Sep/outputs/tables</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TANK_MIN_M2</t>
+          <t>TANK_COMPACTNESS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>TANK_MIN_M2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>UTM</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>EPSG:32643</t>
         </is>
@@ -2202,7 +2209,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="37" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2917,9 +2924,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -2928,10 +2935,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
@@ -2941,12 +2948,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Highway (NH / SH), Habitation, Airport / airbase</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Critical habitat / eco-fragile area</t>
+          <t>Highway (NH / SH), Habitation, Airport / airbase, Critical habitat / eco-fragile area</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:AB169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4616,7 +4618,9 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
     <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4747,6 +4751,16 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>esz_review</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>esz_note</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>other_protected_land</t>
         </is>
       </c>
@@ -5435,7 +5449,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6185,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6912,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7645,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -8367,10 +8381,10 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>Victoria Nature Park at 5.62 km</t>
         </is>
@@ -9105,7 +9119,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -9825,14 +9839,24 @@
           <t>Khijadiya WLS</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>inside ESZ</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>student check 26 Sep: the landfill lies in the eco-sensitive zone of Khijadiya Wildlife Sanctuary (5.4 km)</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10580,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11304,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -12013,10 +12037,10 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
         <is>
           <t>Sarthana Nature Park &amp; Zoo at 11.51 km</t>
         </is>
@@ -12751,7 +12775,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13508,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14241,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -14947,7 +14971,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -15747,9 +15771,9 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -15758,10 +15782,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -15771,12 +15795,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Habitation, Airport / airbase</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Critical habitat / eco-fragile area</t>
+          <t>Habitation, Airport / airbase, Critical habitat / eco-fragile area</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:AB169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16447,7 +16466,9 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
     <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16578,6 +16599,16 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>esz_review</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>esz_note</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>other_protected_land</t>
         </is>
       </c>
@@ -17266,7 +17297,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18033,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18760,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19493,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20229,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -20931,7 +20962,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -21651,14 +21682,24 @@
           <t>Khijadiya WLS</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>breach</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>inside ESZ</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>student check 26 Sep: the landfill lies in the eco-sensitive zone of Khijadiya Wildlife Sanctuary (5.4 km)</t>
         </is>
       </c>
     </row>
@@ -22382,7 +22423,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -23106,7 +23147,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -23839,7 +23880,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -24572,7 +24613,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25346,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -26038,7 +26079,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26809,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011)</t>
+          <t>OSM protected areas (national parks, sanctuaries, reserves) in Gujarat; inside or &lt; 1 km (minimum ESZ, SC order 3 June 2022) = breach; 1-10 km = check the notified ESZ (10 km default, MoEFCC 2011); confirmed inside the ESZ (config.ESZ_REVIEW) = breach</t>
         </is>
       </c>
     </row>
